--- a/Economic modelling/Sectoral Contribution.xlsx
+++ b/Economic modelling/Sectoral Contribution.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://seiorg-my.sharepoint.com/personal/marlon_passos_sei_org/Documents/Documents/KTH PhD/Thesis Work/Task 2/Codes/Economic/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MarlonVieiraPassos\OneDrive - SEI\Documents\KTH PhD\Thesis Work\Task 2\Codes\Github\hydroclimatic-hazards-impacts\Economic modelling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="168" documentId="8_{CC635839-6FDE-48E9-B595-39439B19D2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{761516A6-68EA-4744-9840-671128E42DBE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD3C66E9-7DBB-47F0-9A2E-6D2896698381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{FA86A3B5-0416-489F-A810-8746510D1D77}"/>
   </bookViews>
@@ -191,7 +191,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -273,7 +273,7 @@
       <sheetData sheetId="0">
         <row r="1">
           <cell r="E1">
-            <v>0.65212277000305696</v>
+            <v>0.8011097477199679</v>
           </cell>
         </row>
         <row r="2">
@@ -716,7 +716,7 @@
       </c>
       <c r="E4" s="5">
         <f>[3]Estimations!$E$1</f>
-        <v>0.65212277000305696</v>
+        <v>0.8011097477199679</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>6</v>
